--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/abr-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>18000000</v>
+        <v>20047.08</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>605065</v>
+        <v>673.88</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7611240</v>
+        <v>8476.84</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>31860000</v>
+        <v>35483.34</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>24350000</v>
+        <v>27119.25</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>58976000</v>
+        <v>65683.16</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>37200000</v>
+        <v>41430.64</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>25220000</v>
+        <v>28088.19</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>33843600</v>
+        <v>37692.53</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>41228740</v>
+        <v>45917.56</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3100000</v>
+        <v>3452.55</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>17136000</v>
+        <v>19084.82</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>397930</v>
+        <v>443.19</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10376800</v>
+        <v>11556.92</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>542212400</v>
+        <v>603876.53</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5000000</v>
+        <v>5568.63</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>30288000</v>
+        <v>33732.56</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>250000</v>
+        <v>278.43</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>40500000</v>
+        <v>45105.94</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13937280</v>
+        <v>15522.32</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>100000</v>
+        <v>111.37</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>31237500</v>
+        <v>34790.04</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3150000</v>
+        <v>3508.24</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>181542</v>
+        <v>202.19</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9975000</v>
+        <v>11109.43</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>23000000</v>
+        <v>25615.72</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1090000</v>
+        <v>1213.96</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5760000</v>
+        <v>6415.07</v>
       </c>
     </row>
   </sheetData>
